--- a/media/excel_files/RT-202406.xlsx
+++ b/media/excel_files/RT-202406.xlsx
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>175</v>
       </c>
     </row>
     <row r="6">
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -525,7 +525,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/media/excel_files/RT-202406.xlsx
+++ b/media/excel_files/RT-202406.xlsx
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -525,7 +525,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/media/excel_files/RT-202406.xlsx
+++ b/media/excel_files/RT-202406.xlsx
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -525,7 +525,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
